--- a/rag-mcp/data/corporate/seojun_roasters/ethics_policy.xlsx
+++ b/rag-mcp/data/corporate/seojun_roasters/ethics_policy.xlsx
@@ -367,7 +367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="1" min="1" max="1"/>
@@ -391,40 +391,30 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>company_id</t>
+          <t>document_type</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>document_id</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>section</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>content</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>section</t>
+          <t>source_url</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="H1" s="9" t="inlineStr">
-        <is>
-          <t>source_url</t>
-        </is>
-      </c>
-      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>published_at</t>
         </is>
@@ -438,36 +428,26 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters</t>
+          <t>ethics_policy</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters-ethics_policy</t>
+          <t>서준로스터스 윤리경영 정책</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>ethics_policy</t>
+          <t>노동·안전</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>서준로스터스 윤리경영 정책</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>노동·안전</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
           <t>안전한 업무 환경과 휴식을 존중한다. 직원 과로·희생·산업재해를 빠른 서비스의 재미 요소로 소비하지 않는다.</t>
         </is>
       </c>
-      <c r="H2" s="7" t="str"/>
-      <c r="I2" s="7" t="str"/>
+      <c r="F2" s="7" t="str"/>
+      <c r="G2" s="7" t="str"/>
     </row>
     <row r="3" ht="130" customHeight="1" s="1">
       <c r="A3" s="7" t="inlineStr">
@@ -477,36 +457,26 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters</t>
+          <t>ethics_policy</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters-ethics_policy</t>
+          <t>서준로스터스 윤리경영 정책</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>ethics_policy</t>
+          <t>조달 표현</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>서준로스터스 윤리경영 정책</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>조달 표현</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
           <t>공정무역 인증·농가 소득 보장·아동노동 없는 원두 주장은 적용 원두·업체·기간과 증빙을 확인한다. 증빙이 확인되지 않은 인증·보장 표현은 광고에 사용하지 않는다.</t>
         </is>
       </c>
-      <c r="H3" s="7" t="str"/>
-      <c r="I3" s="7" t="str"/>
+      <c r="F3" s="7" t="str"/>
+      <c r="G3" s="7" t="str"/>
     </row>
     <row r="4" ht="130" customHeight="1" s="1">
       <c r="A4" s="7" t="inlineStr">
@@ -516,36 +486,26 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters</t>
+          <t>ethics_policy</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters-ethics_policy</t>
+          <t>서준로스터스 윤리경영 정책</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>ethics_policy</t>
+          <t>지역사회 지원</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>서준로스터스 윤리경영 정책</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>지역사회 지원</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
           <t>실직·재난·손실을 조롱하는 마케팅을 하지 않는다. 기부 계획과 실제 전달 완료를 구분하고 자료 범위 안에서만 설명한다.</t>
         </is>
       </c>
-      <c r="H4" s="7" t="str"/>
-      <c r="I4" s="7" t="str"/>
+      <c r="F4" s="7" t="str"/>
+      <c r="G4" s="7" t="str"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
